--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487458_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487458_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.049799999999999</v>
+        <v>8.5594</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1612</v>
+        <v>4.5072</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8885</v>
+        <v>4.0523</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1831</v>
+        <v>3.754</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3385</v>
+        <v>1.0714</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8446</v>
+        <v>2.6826</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5634</v>
+        <v>3.1926</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2197</v>
+        <v>1.2026</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3437</v>
+        <v>1.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6197</v>
+        <v>0.5614</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8812</v>
+        <v>-0.1312</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5009</v>
+        <v>0.6926</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7626</v>
+        <v>3.3294</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7626</v>
+        <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1714</v>
+        <v>-0.5667</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6775</v>
+        <v>-0.7281</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5062</v>
+        <v>0.1614</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2754</v>
+        <v>2.0427</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2754</v>
+        <v>2.0427</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9805</v>
+        <v>7.9382</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3025</v>
+        <v>5.2636</v>
       </c>
       <c r="F3" t="n">
-        <v>3.678</v>
+        <v>2.6747</v>
       </c>
       <c r="G3" t="n">
-        <v>3.754</v>
+        <v>6.1831</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0714</v>
+        <v>0.3385</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6826</v>
+        <v>5.8446</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1926</v>
+        <v>5.5634</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2026</v>
+        <v>1.2197</v>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>4.3437</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5614</v>
+        <v>0.6197</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1312</v>
+        <v>-0.8812</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6926</v>
+        <v>1.5009</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3294</v>
+        <v>1.7626</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3294</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1456</v>
+        <v>-0.2829</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9328</v>
+        <v>-0.5752</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2128</v>
+        <v>0.2923</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0427</v>
+        <v>0.2754</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0427</v>
+        <v>0.2754</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.121</v>
+        <v>6.9828</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0902</v>
+        <v>4.1925</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0309</v>
+        <v>2.7903</v>
       </c>
       <c r="G4" t="n">
         <v>6.4876</v>
@@ -766,13 +766,13 @@
         <v>3.3294</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4621</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7546</v>
+        <v>-0.6522</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2925</v>
+        <v>0.0519</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1385</v>
+        <v>6.3537</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1777</v>
+        <v>3.3394</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9608</v>
+        <v>3.0143</v>
       </c>
       <c r="G5" t="n">
         <v>4.495</v>
@@ -844,13 +844,13 @@
         <v>3.3294</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1571</v>
+        <v>-0.9419</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8316</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3255</v>
+        <v>-0.272</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3329</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1521</v>
+        <v>5.161</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0105</v>
+        <v>0.9093</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1416</v>
+        <v>4.2517</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1443</v>
+        <v>-0.1125</v>
       </c>
       <c r="H6" t="n">
-        <v>2.164</v>
+        <v>-0.9112</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9803</v>
+        <v>0.7987</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9788</v>
+        <v>-0.877</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0244</v>
+        <v>-1.1195</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9544</v>
+        <v>0.2425</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1655</v>
+        <v>0.7645</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1396</v>
+        <v>0.2083</v>
       </c>
       <c r="O6" t="n">
-        <v>0.026</v>
+        <v>0.5562</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5253</v>
+        <v>3.1336</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.3544</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.5928</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7261</v>
+        <v>0.2385</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>4.6486</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.5335</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.8389</v>
+        <v>4.7303</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.0699</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0913</v>
+        <v>3.6604</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1125</v>
+        <v>4.1443</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9112</v>
+        <v>2.164</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7987</v>
+        <v>1.9803</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.877</v>
+        <v>3.9788</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1195</v>
+        <v>2.0244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2425</v>
+        <v>1.9544</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7645</v>
+        <v>0.1655</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2083</v>
+        <v>0.1396</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5562</v>
+        <v>0.026</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1336</v>
+        <v>3.5253</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6765</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>-0.7546</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0781</v>
+        <v>0.245</v>
       </c>
       <c r="V7" t="n">
-        <v>4.6486</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5335</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1152</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7176</v>
+        <v>2.2822</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0831</v>
+        <v>1.3182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6345</v>
+        <v>0.9639</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1833</v>
+        <v>3.0997</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1225</v>
+        <v>-1.3464</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0608</v>
+        <v>4.446</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2365</v>
+        <v>2.7539</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5954</v>
+        <v>-0.6006</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3589</v>
+        <v>3.3545</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0532</v>
+        <v>0.3458</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4729</v>
+        <v>-0.7458</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4197</v>
+        <v>1.0916</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7626</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4387</v>
+        <v>-0.6217</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5505</v>
+        <v>-0.4564</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1118</v>
+        <v>-0.1653</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0319</v>
+        <v>2.1135</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5297</v>
+        <v>1.6915</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5022</v>
+        <v>0.422</v>
       </c>
       <c r="G9" t="n">
         <v>2.2986</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2252</v>
+        <v>-0.1437</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.1947</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1312</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8591</v>
+        <v>2.0385</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2159</v>
+        <v>1.3238</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6432</v>
+        <v>0.7147</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0997</v>
+        <v>0.1833</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3464</v>
+        <v>0.1225</v>
       </c>
       <c r="I10" t="n">
-        <v>4.446</v>
+        <v>0.0608</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7539</v>
+        <v>0.2365</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6006</v>
+        <v>0.5954</v>
       </c>
       <c r="L10" t="n">
-        <v>3.3545</v>
+        <v>-0.3589</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3458</v>
+        <v>-0.0532</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7458</v>
+        <v>-0.4729</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0916</v>
+        <v>0.4197</v>
       </c>
       <c r="P10" t="n">
+        <v>1.7626</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.1958</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.9792</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0448</v>
+        <v>-0.2404</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5587</v>
+        <v>-0.2088</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.486</v>
+        <v>-0.0316</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7384</v>
+        <v>1.685</v>
       </c>
       <c r="E11" t="n">
         <v>1.5121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2263</v>
+        <v>0.1729</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1502</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7773</v>
+        <v>-0.8307</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4209</v>
+        <v>-0.4743</v>
       </c>
       <c r="V11" t="n">
         <v>1.8825</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5942</v>
+        <v>0.6744</v>
       </c>
       <c r="E12" t="n">
         <v>0.6367</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0425</v>
+        <v>0.0377</v>
       </c>
       <c r="G12" t="n">
         <v>2.0894</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2163</v>
+        <v>-1.1361</v>
       </c>
       <c r="T12" t="n">
         <v>-0.6952</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5211</v>
+        <v>-0.4409</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4332</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>48.22199999999999</v>
+        <v>48.519</v>
       </c>
       <c r="E13" t="n">
-        <v>25.4671</v>
+        <v>25.7642</v>
       </c>
       <c r="F13" t="n">
-        <v>22.7548</v>
+        <v>22.7549</v>
       </c>
       <c r="G13" t="n">
         <v>32.4723</v>
       </c>
       <c r="H13" t="n">
-        <v>7.488900000000001</v>
+        <v>7.488899999999999</v>
       </c>
       <c r="I13" t="n">
         <v>24.9832</v>
@@ -1468,16 +1468,16 @@
         <v>25.4602</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.525500000000001</v>
+        <v>-6.228400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.1813</v>
+        <v>-5.8843</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3439999999999999</v>
+        <v>-0.344</v>
       </c>
       <c r="V13" t="n">
-        <v>4.6486</v>
+        <v>4.648600000000002</v>
       </c>
       <c r="W13" t="n">
         <v>8.228399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8554</v>
+        <v>2.1357</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1091</v>
+        <v>2.4161</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2536</v>
+        <v>-0.2804</v>
       </c>
       <c r="G14" t="n">
         <v>1.0385</v>
@@ -1546,13 +1546,13 @@
         <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5047</v>
+        <v>0.785</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3388</v>
+        <v>-0.0318</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8435</v>
+        <v>0.8168</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2754</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3182</v>
+        <v>-0.6493</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6204</v>
+        <v>-0.4518</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3023</v>
+        <v>-0.1975</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.7453</v>
+        <v>-2.7701</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3611</v>
+        <v>-0.5168</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3841</v>
+        <v>-2.2532</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5681</v>
+        <v>-0.3441</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4064</v>
+        <v>0.2977</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1617</v>
+        <v>-0.6418</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.3134</v>
+        <v>-2.4259</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7676</v>
+        <v>-0.8145</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5458</v>
+        <v>-1.6114</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1292</v>
+        <v>0.3973</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5764</v>
+        <v>-0.1076</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5528</v>
+        <v>0.5049</v>
       </c>
       <c r="V15" t="n">
-        <v>1.501</v>
+        <v>1.3318</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4344</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1229</v>
+        <v>-0.8612</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4735</v>
+        <v>-1.5758</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3506</v>
+        <v>0.7146</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5329</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1554</v>
+        <v>1.4171</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2329</v>
+        <v>-0.3352</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3883</v>
+        <v>1.7524</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9412</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.323</v>
+        <v>-2.2227</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0424</v>
+        <v>1.2667</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2805</v>
+        <v>-3.4894</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7701</v>
+        <v>-3.7453</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5168</v>
+        <v>-1.3611</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2532</v>
+        <v>-2.3841</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3441</v>
+        <v>0.5681</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2977</v>
+        <v>0.4064</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6418</v>
+        <v>0.1617</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4259</v>
+        <v>-4.3134</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8145</v>
+        <v>-1.7676</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6114</v>
+        <v>-2.5458</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7236</v>
+        <v>1.5884</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3017</v>
+        <v>1.2227</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4219</v>
+        <v>0.3657</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3318</v>
+        <v>1.501</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="X17" t="n">
-        <v>1.3318</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8821</v>
+        <v>-2.9132</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4409</v>
+        <v>-0.9292</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4412</v>
+        <v>-1.984</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0759</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2437</v>
+        <v>0.7252</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3805</v>
+        <v>0.1312</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1368</v>
+        <v>0.594</v>
       </c>
       <c r="V18" t="n">
         <v>-2.3666</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.9787</v>
+        <v>-5.6375</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0458</v>
+        <v>-3.8412</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9328</v>
+        <v>-1.7964</v>
       </c>
       <c r="G19" t="n">
         <v>-3.785</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3147</v>
+        <v>0.0265</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6952</v>
+        <v>-0.4905</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3805</v>
+        <v>0.517</v>
       </c>
       <c r="V19" t="n">
         <v>0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8737</v>
+        <v>-6.1464</v>
       </c>
       <c r="E20" t="n">
         <v>-3.9724</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9013</v>
+        <v>-2.174</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5978</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1435</v>
+        <v>0.5839</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1735</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0301</v>
+        <v>0.7574</v>
       </c>
       <c r="V20" t="n">
         <v>0.8260999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.9789</v>
+        <v>-8.1006</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.908</v>
+        <v>-4.1127</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0709</v>
+        <v>-3.988</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7602</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3112</v>
+        <v>1.1895</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5681</v>
+        <v>0.3635</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7431</v>
+        <v>0.826</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3756</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.3165</v>
+        <v>-9.245200000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.5471</v>
+        <v>-6.9331</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7694</v>
+        <v>-2.3121</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8169999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7125</v>
+        <v>0.3588</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6534</v>
+        <v>-0.0394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.059</v>
+        <v>0.3982</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5405</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.3763</v>
+        <v>-10.4212</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7044</v>
+        <v>-4.8857</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.672</v>
+        <v>-5.5355</v>
       </c>
       <c r="G23" t="n">
         <v>-6.3093</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1958</v>
+        <v>0.7593</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0339</v>
+        <v>-0.2153</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8381</v>
+        <v>0.9745</v>
       </c>
       <c r="V23" t="n">
         <v>-1.15</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.6785</v>
+        <v>-44.0616</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.405</v>
+        <v>-23.0191</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.2734</v>
+        <v>-21.0427</v>
       </c>
       <c r="G24" t="n">
         <v>-29.355</v>
@@ -2299,7 +2299,7 @@
         <v>-22.3821</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.462199999999999</v>
+        <v>-1.4622</v>
       </c>
       <c r="K24" t="n">
         <v>1.5032</v>
@@ -2326,13 +2326,13 @@
         <v>7.638</v>
       </c>
       <c r="S24" t="n">
-        <v>7.213899999999999</v>
+        <v>7.831</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9380000000000002</v>
+        <v>0.3241</v>
       </c>
       <c r="U24" t="n">
-        <v>6.2761</v>
+        <v>7.5069</v>
       </c>
       <c r="V24" t="n">
         <v>-4.715</v>
